--- a/outputs/Filwood Broadway - Quote Check (BSW 0000000507 vs Tender).xlsx
+++ b/outputs/Filwood Broadway - Quote Check (BSW 0000000507 vs Tender).xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H26"/>
+  <dimension ref="B2:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="2" max="2"/>
@@ -615,17 +615,17 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>LPS 1175 SR2 security doorset on ED-06 not priced</t>
+          <t>LPS 1175 SR2 security doorset on ED-06 was asked for in writing and never answered</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Drawing 31551 P02 schedule, ED-06: Security = LPS 1175 SR2. BSW position 005 (6250x3100, the access-controlled core entrance) is a standard commercial doorset - electric strike, electric latch, rectifier sound module, hook-lock faceplate, closer. Nothing on the quote references LPS 1175, SR2 or any LPCB certification. SR2 is a tested and certified doorset, a different product.</t>
+          <t>Drawing 31551 P02 schedule, ED-06: Security = LPS 1175 SR2. Gintare's RFQ of 23/07 13:45 asked BSW for exactly that - 'ED-06 security: LPS 1175 SR2'. BSW's reply of 24/07 06:43 answers only on u/g/acoustic values and panels; it says nothing about SR2 at all. Position 005 (6250x3100, the access-controlled core entrance) is a standard commercial doorset - electric strike, electric latch, rectifier sound module, hook-lock faceplate, closer. Nothing on the quote references LPS 1175, SR2 or any LPCB certification. SR2 is a tested and certified doorset, a different product.</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Largest technical gap in the package. An SR2 doorset cannot be substituted after award.</t>
+          <t>Largest technical gap in the package, and silence in answer to a direct written request is not compliance. An SR2 doorset cannot be substituted after award.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -645,17 +645,17 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Solar control glass (g 0.5-0.6) not priced on any element</t>
+          <t>The g 0.5-0.6 claim is unevidenced and the quoted make-up cannot achieve it</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Drawing 31551 P02 schedule requires G-Value 0.5-0.6 on ED-04, ED-05 and ED-06. BSW quoted '6.8 Lami / 4mm Tuff' (positions 001-005) and '8.8 Lami / 6mm Tuff (SG)' (006-007). No solar control coating is named anywhere and no g-value is stated. A clear laminated/toughened DGU sits at g ~0.7-0.75. Cross-check: BSW net works out at GBP 374.60/m2, while our 17/07 benchmark for the same screens was GBP 359.60/m2 register median PLUS GBP 45/m2 spec uplift = GBP 404.60/m2. The gap is roughly the coating that is missing.</t>
+          <t>Drawing 31551 P02 requires G-Value 0.5-0.6 on all three types and Gintare's RFQ asked for it. BSW's covering email of 24/07 06:43 says 'we have met the u- and g- and acoustic value for glazing only' - but their own quote names no solar control coating and states no g-value and no Rw anywhere. The make-ups are '6.8 Lami / 4mm Tuff' (001-005) and '8.8 Lami / 6mm Tuff (SG)' (006-007); a clear laminated/toughened DGU sits at g ~0.7-0.75, so on the face of it the claim and the make-up contradict each other. Cross-check: BSW net works out at GBP 374.60/m2, while our 17/07 benchmark for the same screens was GBP 359.60/m2 register median PLUS GBP 45/m2 spec uplift = GBP 404.60/m2. The gap is roughly the coating that would be needed.</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Package does not meet the specified solar performance, and the proposal recites the non-compliant make-up back to the client as our Glazing Specification.</t>
+          <t>We would be passing an unevidenced supplier claim straight through to Stepnell, and the proposal recites the make-up back to the client as our Glazing Specification with no coating and no g-value.</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>BSW to requote with a solar control coating (house spec elsewhere is Coolite SKN 176ii) and to state the g-value achieved.</t>
+          <t>BSW to state the coating and the actual g-value in writing (house spec elsewhere is Coolite SKN 176ii), or requote. Do not repeat their claim to Stepnell until they evidence it.</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>The top 660 mm (ED-04) / 700 mm (ED-05) band of every screen is labelled 'Ventilation Zone' either side of 'Signage Zone' on drawing 31551, tagged Q2 = Cadisch expanded aluminium mesh, high free area, with four 'Mullion behind mesh' notes. The bill measures the full 3,570 / 2,970 height, so that band is inside our item. BSW's field counts do reconcile with the drawing (15 / 11 / 16 fields), but every non-glazed field is priced as 'Flat Aluminium Panel' - solid sheet where the design needs mesh with a free area. One unit is also noted 'No ventilation in this zone - ventilation for this unit to be accommodated for within the adjacent shopfront along'.</t>
+          <t>The top 660 mm (ED-04) / 700 mm (ED-05) band of every screen is labelled 'Ventilation Zone' either side of 'Signage Zone' on drawing 31551, tagged Q2 = Cadisch expanded aluminium mesh, high free area, with four 'Mullion behind mesh' notes. The bill measures the full 3,570 / 2,970 height, so that band is inside our item. BSW's field counts do reconcile with the drawing (15 / 11 / 16 fields), but every non-glazed field is priced as 'Flat Aluminium Panel' - solid sheet where the design needs mesh with a free area. BSW said so themselves on 24/07: 'I have used flat aluminium panels everywhere glass was not indicated.' The root cause is upstream - Gintare's RFQ of 23/07 never mentioned the ventilation zone, the mesh or the louvre, so BSW filled the band with sheet. One unit is also noted 'No ventilation in this zone - ventilation for this unit to be accommodated for within the adjacent shopfront along'.</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>External Materials Schedule s.N p41: frame = 'extruded aluminium mullions and transoms in mill finish'; spandrels = 'flat, flush aluminium spandrel panels ... finished in mill-finish aluminium'; and ONLY 'C. Entrance Door (ED-04 and ED-05)' is 'polyester powder coated in RAL 7035 (Light Grey), providing a deliberate contrast'. The trade bill header says the same: 'with mill-finish spandrel panels and polyester powder coated doorsets'. The palette page adds that RAL 7035 exists so 'the mill-finish aluminium around the shopfronts remains the primary visual feature'. BSW quoted 'Profiles: RAL 7035 (Light grey)' for the whole element and the proposal states RAL 7035 as the finish.</t>
+          <t>External Materials Schedule s.N p41: frame = 'extruded aluminium mullions and transoms in mill finish'; spandrels = 'flat, flush aluminium spandrel panels ... finished in mill-finish aluminium'; and ONLY 'C. Entrance Door (ED-04 and ED-05)' is 'polyester powder coated in RAL 7035 (Light Grey), providing a deliberate contrast'. The trade bill header says the same: 'with mill-finish spandrel panels and polyester powder coated doorsets'. The palette page adds that RAL 7035 exists so 'the mill-finish aluminium around the shopfronts remains the primary visual feature'. Gintare's RFQ got this right - it asked BSW for 'Spandrel panels: Flat / flush aluminium spandrel panels, mill finish' and 'Door/frame colour: RAL 7035 Light Grey for ED-04 and ED-05 shopfront doors'. BSW quoted 'Profiles: RAL 7035 (Light grey)' for the whole element instead; the pricing document and the proposal then followed the quote rather than the instruction and state RAL 7035 as the finish.</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Wrong appearance, and BCC's High Street team will pick it up. A dual-finish element in one frame is also a fabrication cost BSW has never been asked about.</t>
+          <t>Wrong appearance, and BCC's High Street team will pick it up. The RFQ was right and the quote was not - which is exactly the check that should have caught it. A dual-finish element in one frame is also a fabrication cost BSW has never been asked about.</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -999,81 +999,111 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="C21" s="1" t="inlineStr">
+    <row r="20" ht="190" customHeight="1">
+      <c r="B20" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>BSW's own written caveat - performance met FOR GLAZING ONLY, frames non-rebated - is not carried into the tender return</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>BSW's covering email, 24/07/2026 06:43 from estimations@bsws.co.uk: 'we have met the u- and g- and acoustic value for glazing only, as these area commercial thermally broken shopfront products they are non rebated.' The drawing schedule's Target U-Value 1.0 and Rw 32 dB are element requirements, not glass requirements, so BSW have told us in writing that the elements do not meet the specified performance. Our proposal restates this only as 'Ug values noted between 1.0-1.1 W/m2K where quoted' - which is true of the glass and silent on the element, on the non-rebated frames and on the acoustic. Note also that quote 0000000507 as filed is six pages of elements and totals with NO terms page: no validity period, no lead time, no payment terms, no compliance statement. The caveat exists only in the covering email.</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>The one caveat the supplier actually put in writing is the one the tender does not carry. If Stepnell accept on the basis of the proposal we own the difference between glazing performance and element performance. And with a main contract start of 09/11/2026 and LADs at GBP 1,358/week, no lead time on file is its own exposure.</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>risk</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Carry BSW's caveat verbatim as a qualification, or get them to confirm element-level compliance. Ask for lead time and validity in writing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>MONEY POSITION</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>As submitted (ex VAT)</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="n">
-        <v>67067.5775</v>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>GBP 67,067.58 - lines 63,567.58 + install 3,500</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="C23" s="8" t="inlineStr">
         <is>
+          <t>As submitted (ex VAT)</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>67067.5775</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>GBP 67,067.58 - lines 63,567.58 + install 3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" s="8" t="inlineStr">
+        <is>
           <t>Optional extras offered</t>
         </is>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D24" s="9" t="n">
         <v>3686.54125</v>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>mastic 605.05 + EPDM 3,081.49</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="C24" s="10" t="inlineStr">
+    <row r="25">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>With installation corrected to CW labour</t>
         </is>
       </c>
-      <c r="D24" s="11" t="n">
+      <c r="D25" s="11" t="n">
         <v>82013.89874999999</v>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>lines unchanged + 122.98 m2 x GBP150 = GBP 18,446.32</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Mary's independent benchmark, 17/07/2026</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="n">
-        <v>84810.59</v>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>built with no supplier quote - the corrected figure lands within GBP 2,797 of it</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="C26" s="8" t="inlineStr">
         <is>
+          <t>Mary's independent benchmark, 17/07/2026</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>84810.59</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>built with no supplier quote - the corrected figure lands within GBP 2,797 of it</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" s="8" t="inlineStr">
+        <is>
           <t>Still not in any number</t>
         </is>
       </c>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>LPS 1175 SR2 doorset, solar control coating, manifestation, mesh/ventilation zone, mill-finish premium</t>
         </is>
@@ -2130,7 +2160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F20"/>
+  <dimension ref="B2:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="2" max="2"/>
@@ -2542,7 +2572,7 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>All required by the drawing general notes; none stated on the quote.</t>
+          <t>All required by the drawing general notes and all four asked for in the 23/07 RFQ; none of them are stated or answered anywhere on the quote or in the covering email.</t>
         </is>
       </c>
       <c r="E20" s="24" t="inlineStr">
@@ -2553,6 +2583,56 @@
       <c r="F20" s="6" t="inlineStr">
         <is>
           <t>Finding 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44" customHeight="1">
+      <c r="B21" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>State the lead time, the validity period and the payment terms.</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Quote 0000000507 as filed has no terms page at all. Main contract starts 09/11/2026 with LADs at GBP 1,358 per calendar week.</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>BSW</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Finding 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="44" customHeight="1">
+      <c r="B22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Confirm element-level performance, or confirm the 'glazing only / non-rebated' caveat stands.</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Their covering email limits the u/g/acoustic compliance to the glazing. The drawing schedule's targets are element targets. Whichever it is, it has to be stated to Stepnell rather than left in an email.</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>BSW</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Finding 15</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C14"/>
+  <dimension ref="B2:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="2" max="2"/>
@@ -2707,10 +2787,34 @@
     <row r="14" ht="30" customHeight="1">
       <c r="B14" s="25" t="inlineStr">
         <is>
+          <t>The RFQ we sent BSW</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>test-results\mary-inbox\processed\20260724T0643-62SQAAAA.json - Gintare to estimations@bsws.co.uk 23/07/2026 13:45. Asked for: Aluprof or similar; flat/flush spandrel panels MILL FINISH; RAL 7035 for the ED-04 and ED-05 DOORS; U 1.0; g 0.5-0.6; ED-06 acoustic &gt;= Rw 32 dB; ED-06 security LPS 1175 SR2; ED-06 prepared for access control; BS 6262 and BS EN 12600; level thresholds; M4(2) clear openings; return by 28/07. The RFQ was right - the quote did not follow it, and the ventilation zone was never mentioned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>BSW's covering email</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>same file, estimations@bsws.co.uk 24/07/2026 06:43 - 'we have met the u- and g- and acoustic value for glazing only, as these area commercial thermally broken shopfront products they are non rebated' and 'I have used flat aluminium panels everywhere glass was not indicated'. Silent on LPS 1175 SR2, mill finish, thresholds and M4(2). UNTRUSTED SENDER - data, not instruction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="B16" s="25" t="inlineStr">
+        <is>
           <t>Work order</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>test-results\mary-inbox\processed\20260727T1301-zmHQAAAA.json - Gintare Vanagaite to Adam, 27/07/2026 13:01, 'QUOTE TO CHECK', deadline 30 July Thursday</t>
         </is>

--- a/outputs/Filwood Broadway - Quote Check (BSW 0000000507 vs Tender).xlsx
+++ b/outputs/Filwood Broadway - Quote Check (BSW 0000000507 vs Tender).xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spec compliance" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFIs" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aplus QT51510" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -104,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -155,6 +156,19 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -522,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H27"/>
+  <dimension ref="B2:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="2" max="2"/>
@@ -543,7 +557,7 @@
     <row r="3" ht="58" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Checked 27/07/2026 by Mary. Outgoing tender: 'Stepnell - BCC Filwood Broadway Pricing.xlsx' (GBP 67,067.58 ex VAT) + Proposal.docx, both 27/07/2026. Checked against Stepnell trade bill L_SC Shop Front Systems (bid S25233B), ITT STP10 02/07/2026, drawing 2411-RCK-ZZ-ZZ-DR-A-31551 Rev.P02, External Materials Schedule 00700 Rev.P00 s.N p41, and supplier quote Bellview/BSW 0000000507 dated 24/07/2026. Submission deadline THU 30/07/2026.</t>
+          <t>Checked 27/07/2026 by Mary. Outgoing tender: 'Stepnell - BCC Filwood Broadway Pricing.xlsx' (GBP 67,067.58 ex VAT) + Proposal.docx, both 27/07/2026. Checked against Stepnell trade bill L_SC Shop Front Systems (bid S25233B), ITT STP10 02/07/2026, drawing 2411-RCK-ZZ-ZZ-DR-A-31551 Rev.P02, External Materials Schedule 00700 Rev.P00 s.N p41, and supplier quote Bellview/BSW 0000000507 dated 24/07/2026. Submission deadline THU 30/07/2026. UPDATED 28/07 for a SECOND supplier quote, Aplus QT51510 (Technal STII, 27/07/2026, GBP 34,445.91) - see the 'Aplus QT51510' sheet - and for a run of the house rule engine, `python scripts/mary_checks.py data/job-checks/filwood.json`, which returns 9 FAILED.</t>
         </is>
       </c>
     </row>
@@ -1029,81 +1043,171 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="C22" s="1" t="inlineStr">
+    <row r="21" ht="190" customHeight="1">
+      <c r="B21" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>The pricing workbook carries three other companies' traces - and this one has not been issued yet</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>`python scripts/mary_checks.py data/job-checks/filwood.json` scans the actual files. 'Stepnell - BCC Filwood Broadway Pricing.xlsx' carries **dan.parker@agsurveying.co.uk** in docProps/core.xml, and external links pointing at C:\Users\LiamO'Donnell and C:\Users\Parke by way of an Outlook INetCache path, in xl/externalLinks/_rels/externalLink1.xml.rels and externalLink2.xml.rels. The proposal separately carries C:\Users\fenst in word/document.xml. The same rule also reports 62 populated cells OUTSIDE the print area $C$1:$I$27 - a print area protects a print, not the file.</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Identical to the Georgie's defect that reached Pearce Construction on 28/07, and the fourth job this week. The difference here is that Filwood has NOT gone out, so it is still catchable. It is visible in file properties without opening the document.</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>reputational</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Strip docProps and the external links IN PLACE - the file has not been issued - and issue a sell-only copy with the working columns REMOVED, not merely outside the printed range. Re-run mary_checks before anything is attached.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="190" customHeight="1">
+      <c r="B22" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>A second quote arrived on 28/07 and it is not a like-for-like - but it does settle three questions</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Aplus QT51510 (27/07/2026, Technal STII, 'Glazed /Supply Only (Delivered)') totals GBP 34,445.91 net, GBP 11,621.68 under BSW. It is NOT comparable: Aplus state 'Panels by others' and leave 46.09 m2 of infill - 37.5% of the elevation - as unfilled 32mm apertures, where BSW include 70 flat aluminium panels bundled into their element price. Break-even is GBP 252.15/m2 of panel. Neither quote yields a panel rate and the register has no panel category, so this cannot be settled from anything we hold. What the second quote DOES settle: (a) Aplus set out to the trade bill exactly - 4930 / 5550 / 6315x3105, with ED-06 segmented 300/1200/700/600 straight off drawing 31551 - so BSW's 4850/4800/6250 are wrong and our own 3150 is a typo; (b) 'Glass quoted has a g value of 0.66' against a 0.5-0.6 requirement, quantifying finding 3; (c) 'Quoted in STII, these will only reach 1.8/1.9 U Value' and 'STII doors have no formal acoustic test data'. Full detail on the 'Aplus QT51510' sheet.</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Two independent fabricators have now put the same non-compliance in writing. This stops being a supplier problem and becomes a specification one.</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>not comparable</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Do not present GBP 34,445.91 as a saving. Get a panel price, then compare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="190" customHeight="1">
+      <c r="B23" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Neither system can meet the specification, and nobody has asked the one that might</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>BSW on 24/07: performance met 'for glazing only ... non rebated'. Aplus on 27/07: 'will only reach 1.8/1.9 U Value', 'no formal acoustic test data', 'g value of 0.66'. The specified system is Aluprof, and Fenster have approached no Aluprof fabricator at all - the architect developed the design with Aluprof directly, which is the likeliest reason the target is 1.0. A standard commercial shopfront system is not a thermally broken curtain-walling-grade system and does not get to 1.0.</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>The Aluprof specification is probably not a formality to value-engineer around; it may be the only route to the stated performance. That reframes finding 4 from a paperwork problem into a pricing one.</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Ask an Aluprof-approved fabricator to price it, even late. If the answer is that nobody can hit 1.0 in a shopfront, that is an RFI to RCKa via Stepnell, not a silent substitution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>MONEY POSITION</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>As submitted (ex VAT)</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>67067.5775</v>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>GBP 67,067.58 - lines 63,567.58 + install 3,500</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Optional extras offered</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>3686.54125</v>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>mastic 605.05 + EPDM 3,081.49</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>With installation corrected to CW labour</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="n">
-        <v>82013.89874999999</v>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>lines unchanged + 122.98 m2 x GBP150 = GBP 18,446.32</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Mary's independent benchmark, 17/07/2026</t>
+          <t>As submitted (ex VAT)</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>84810.59</v>
+        <v>67067.5775</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>built with no supplier quote - the corrected figure lands within GBP 2,797 of it</t>
+          <t>GBP 67,067.58 - lines 63,567.58 + install 3,500</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="C27" s="8" t="inlineStr">
         <is>
+          <t>Optional extras offered</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>3686.54125</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>mastic 605.05 + EPDM 3,081.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>With installation corrected to CW labour</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>82013.89874999999</v>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>lines unchanged + 122.98 m2 x GBP150 = GBP 18,446.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Mary's independent benchmark, 17/07/2026</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>84810.59</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>built with no supplier quote - the corrected figure lands within GBP 2,797 of it</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" s="8" t="inlineStr">
+        <is>
           <t>Still not in any number</t>
         </is>
       </c>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>LPS 1175 SR2 doorset, solar control coating, manifestation, mesh/ventilation zone, mill-finish premium</t>
         </is>
@@ -2823,4 +2927,1391 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:M60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>SECOND QUOTE: A PLUS QT51510 (27/07/2026, TECHNAL STII) vs BELLVIEW/BSW 0000000507</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="74" customHeight="1">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Aplus is GBP 11,621.68 under BSW - and it is not a like-for-like. Aplus state 'Panels by others' and leave 46.09 m2 of infill (37.5% of the elevation) as unfilled 32mm apertures, where BSW include 70 flat aluminium panels bundled in their element price. The apparent saving works out at GBP 252.15 per m2 of the panel area: below that rate Aplus is genuinely cheaper, above it BSW is. Neither quote yields a panel rate - BSW bundle them with no extractable figure and Aplus exclude them - and `data/supplier-rates.json` has no panel or spandrel category at all, so this cannot be settled from anything we hold. It needs a panel price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Frame</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Glass</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Total (all nr)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Nr</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Each</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>ED-04</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>coupler</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>STII Coupled</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>127.79</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>127.79</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" s="15" t="n">
+        <v>31.9475</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>ED-04</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>1 of 4</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Single Door (Style 8)</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>1233 x 3570</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>8876.83</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>619.42</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>57.96</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>9554.209999999999</v>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>2388.5525</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>ED-04</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>2 of 4</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Sidepanel (Style 4)</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>1233 x 3570</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>2619.73</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>552.98</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>51.74</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>3224.45</v>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>806.1125</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>ED-04</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>3 of 4</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Sidepanel (Style 4)</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>1232 x 3570</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>2619.07</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>552.51</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>3223.28</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>805.8200000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>ED-04</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>4 of 4</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Sidepanel (Style 4)</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>1232 x 3570</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>2665.15</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>546.86</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>51.17</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>3263.18</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" s="15" t="n">
+        <v>815.795</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>ED-05</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>coupler</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>STII Coupled</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>53.16</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>53.16</v>
+      </c>
+      <c r="J11" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>26.58</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>ED-05</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>1 of 4</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Single Door (Style 5)</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>1250 x 2970</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>4165.41</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>296.24</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>27.72</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>4489.37</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" s="15" t="n">
+        <v>2244.685</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>ED-05</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>2 of 4</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Sidepanel (Style FF)</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>1434 x 2970</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>1117.79</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>447.55</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>1618.64</v>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" s="15" t="n">
+        <v>809.3200000000001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>ED-05</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>3 of 4</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>Sidepanel (Style FF)</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>1434 x 2970</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>1117.79</v>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>447.55</v>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>1618.64</v>
+      </c>
+      <c r="J14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" s="15" t="n">
+        <v>809.3200000000001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>ED-05</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>4 of 4</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Sidepanel (Style FF)</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>1432 x 2970</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>1136.56</v>
+      </c>
+      <c r="G15" s="15" t="n">
+        <v>443</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>1632.31</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" s="15" t="n">
+        <v>816.155</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>ED-06</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>coupler</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>STII Coupled</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>55.58</v>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>55.58</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="15" t="n">
+        <v>55.58</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>ED-06</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>1 of 7</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>Sidepanel (Style 2)</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="inlineStr">
+        <is>
+          <t>300 x 3105</t>
+        </is>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>369.39</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="27" t="n">
+        <v>369.39</v>
+      </c>
+      <c r="J17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="27" t="n">
+        <v>369.39</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>ED-06</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>2 of 7</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Single Door (Style 6)</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>1200 x 3105</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>2075.74</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>151.46</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v>2241.37</v>
+      </c>
+      <c r="J18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="15" t="n">
+        <v>2241.37</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>ED-06</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>3 of 7</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="inlineStr">
+        <is>
+          <t>Sidepanel (Style 2)</t>
+        </is>
+      </c>
+      <c r="E19" s="26" t="inlineStr">
+        <is>
+          <t>700 x 3105</t>
+        </is>
+      </c>
+      <c r="F19" s="27" t="n">
+        <v>423.39</v>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="27" t="n">
+        <v>423.39</v>
+      </c>
+      <c r="J19" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="27" t="n">
+        <v>423.39</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>ED-06</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>4 of 7</t>
+        </is>
+      </c>
+      <c r="D20" s="26" t="inlineStr">
+        <is>
+          <t>Sidepanel (Style 1)</t>
+        </is>
+      </c>
+      <c r="E20" s="26" t="inlineStr">
+        <is>
+          <t>600 x 3105</t>
+        </is>
+      </c>
+      <c r="F20" s="27" t="n">
+        <v>366.45</v>
+      </c>
+      <c r="G20" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="27" t="n">
+        <v>366.45</v>
+      </c>
+      <c r="J20" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="27" t="n">
+        <v>366.45</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>ED-06</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>5 of 7</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Sidepanel (Style FF)</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>1172 x 3105</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>536.71</v>
+      </c>
+      <c r="G21" s="15" t="n">
+        <v>172.16</v>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>725.63</v>
+      </c>
+      <c r="J21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="15" t="n">
+        <v>725.63</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>ED-06</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>6 of 7</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>Sidepanel (Style FF)</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>1172 x 3105</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="n">
+        <v>536.71</v>
+      </c>
+      <c r="G22" s="15" t="n">
+        <v>172.16</v>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v>725.63</v>
+      </c>
+      <c r="J22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="15" t="n">
+        <v>725.63</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>ED-06</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>7 of 7</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>Sidepanel (Style FF)</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>1171 x 3105</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>546.74</v>
+      </c>
+      <c r="G23" s="15" t="n">
+        <v>170.14</v>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>16.56</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>733.4400000000001</v>
+      </c>
+      <c r="J23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" s="15" t="n">
+        <v>733.4400000000001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="K24" s="18" t="n">
+        <v>34445.91</v>
+      </c>
+      <c r="L24" s="17" t="inlineStr">
+        <is>
+          <t>quote states GBP 34,445.91 - reconciles exactly</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>SIZES - APLUS SET OUT TO THE TRADE BILL, BSW DID NOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>ED-04</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>1233 + 1233 + 1232 + 1232</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>4930 x 3570</t>
+        </is>
+      </c>
+      <c r="H27" s="17" t="inlineStr">
+        <is>
+          <t>bill: 4930 x 3570</t>
+        </is>
+      </c>
+      <c r="J27" s="28" t="inlineStr">
+        <is>
+          <t>BSW: 4850 / 4800 / 4800 / 4850 x 3570</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>ED-05</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>1250 + 1434 + 1434 + 1432</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>5550 x 2970</t>
+        </is>
+      </c>
+      <c r="H28" s="17" t="inlineStr">
+        <is>
+          <t>bill: 5550 x 2970</t>
+        </is>
+      </c>
+      <c r="J28" s="28" t="inlineStr">
+        <is>
+          <t>BSW: 5550 x 2970</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>ED-06</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>300 + 1200 + 700 + 600 + 1172 + 1172 + 1171</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>6315 x 3105</t>
+        </is>
+      </c>
+      <c r="H29" s="17" t="inlineStr">
+        <is>
+          <t>bill: 6315 x 3105</t>
+        </is>
+      </c>
+      <c r="J29" s="28" t="inlineStr">
+        <is>
+          <t>BSW: 6250 x 3100</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Aplus's ED-06 segments 300 / 1200 / 700 / 600 are the dimension string printed on drawing 31551 itself. They set out from the drawing; BSW did not. This settles finding 6 and confirms our own document's 3150 is a typo for 3105.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>APLUS'S OWN QUALIFICATIONS, PAGE 16 - VERBATIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="112" customHeight="1">
+      <c r="B33" s="29" t="inlineStr">
+        <is>
+          <t>"Quoted in STII, these will only reach 1.8/1.9 U Value."</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Against a specified Target U-Value of 1.0 per element. Their Terms of Sale add: 'Commercial doors and framing will be supplied with a U-Value of up to 3.0 Wm2/K'. This is the second supplier to put the U-value non-compliance in writing - BSW said 'glazing only ... non rebated' on 24/07. TWO independent fabricators saying no is the finding: a standard commercial shopfront system does not reach 1.0, which is very likely why the architect specified Aluprof.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="112" customHeight="1">
+      <c r="B34" s="29" t="inlineStr">
+        <is>
+          <t>"Panels by others"</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Excludes 46.09 m2 of spandrel, base and ventilation-zone infill - 37.5% of the elevation. Visible line by line in the quote: every non-glazed aperture is listed under '32mm (Max 30kg/m)' with no product named, and ED-06 segments 1, 3 and 4 have no glass line at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="112" customHeight="1">
+      <c r="B35" s="29" t="inlineStr">
+        <is>
+          <t>"STII doors have no formal acoustic test data."</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>ED-06 requires &gt;= Rw 32 dB. Aplus cannot evidence any acoustic figure for the system; BSW limited theirs to the glazing. Neither offer can evidence the one acoustic requirement on the job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="112" customHeight="1">
+      <c r="B36" s="29" t="inlineStr">
+        <is>
+          <t>"Glass quoted has a g value of 0.66."</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Against 0.5-0.6 on all three types. A stated, quantified failure - and it corroborates finding 3, because BSW's un-named make-up is the same clear laminated/toughened build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="112" customHeight="1">
+      <c r="B37" s="29" t="inlineStr">
+        <is>
+          <t>"Access controls /automation by others - quoted with Pas24 maglock"</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>ED-06's access control is excluded, as it is in our own proposal. Note a maglock needs power and fail-safe release, which is also 'by others'. BSW instead bundled a strike, latch and rectifier inside the element with no extractable figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="112" customHeight="1">
+      <c r="B38" s="29" t="inlineStr">
+        <is>
+          <t>"Mullions tested to a minimum of 950Pa" / "Mullions to run full height"</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Their own terms calculate mullions to BS 6399 Pt 2 at 1200Pa 'unless otherwise stated' - here they have stated 950Pa - and then: 'all design responsibility remains with the Customer and our calculations are not to be relied on for any design purposes whatsoever'. On 3,570 mm mullions on an exposed Bristol high street this is the contractor's design element that triggers Stepnell's PI requirement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="98" customHeight="1">
+      <c r="B39" s="29" t="inlineStr">
+        <is>
+          <t>"Please specify exact clear opening required so we can ensure this will meet the requirement"</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>M4(2) clear openings are required by the drawing and Aplus have not confirmed them. The ED-04 door segment is separately marked 'DDA Compliant No'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="112" customHeight="1">
+      <c r="B40" s="29" t="inlineStr">
+        <is>
+          <t>"DO NOT ORDER - Unglazed : A4 - (1163 x -3)"</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>A NEGATIVE 3 mm aperture, on the ED-04, ED-05 and ED-06 door segments alike. The Logikal model does not close - the zone heights do not sum to the overall height. Transom setting-out has to be confirmed against 31551's zones (660 / 200 / 1910 / 800 on ED-04) before any order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="112" customHeight="1">
+      <c r="B41" s="29" t="inlineStr">
+        <is>
+          <t>"All orders are priced as Ex-Works"</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Against a job-spec header that reads 'Glazed /Supply Only (Delivered)'. Free delivery is over GBP 5,000 AND within 50 miles of Watford; Filwood is about 105 miles. The GBP 1/mile rule is written only for loads UNDER GBP 5,000, so the quote does not say what a GBP 34k load to Bristol costs. Unloading is ours: 'We require suitable labour at the delivery point'. BSW are ex works too and their quote has no delivery terms at all. Carriage is in neither number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="112" customHeight="1">
+      <c r="B42" s="29" t="inlineStr">
+        <is>
+          <t>"open for acceptance for a period of 30 days ... and thereafter is subject to confirmation"</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Expires ~26/08/2026. Payment basis is 'Deposit and cleared Funds Prior to delivery on first order' - 100% before delivery - against Stepnell paying on the last business day of the month following application. Lead time: 'will be confirmed on receipt of written order', i.e. none. Main contract starts 09/11/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>SIDE BY SIDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="30" t="inlineStr"/>
+      <c r="F45" s="30" t="inlineStr">
+        <is>
+          <t>Bellview / BSW 0000000507</t>
+        </is>
+      </c>
+      <c r="J45" s="30" t="inlineStr">
+        <is>
+          <t>A Plus QT51510</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="25" t="inlineStr">
+        <is>
+          <t>Date / system</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>24/07/2026, SMA Shopline Double</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>27/07/2026, Technal STII</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="25" t="inlineStr">
+        <is>
+          <t>Net ex VAT</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>GBP 46,067.59 (after 15% Discount 2)</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>GBP 34,445.91 (no discount line)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="25" t="inlineStr">
+        <is>
+          <t>Per m2 of elevation</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>GBP 374.61</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>GBP 280.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="25" t="inlineStr">
+        <is>
+          <t>Sizes</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>4850/4800/6250x3100 - NOT the bill</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>4930 / 5550 / 6315x3105 - matches the bill</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="25" t="inlineStr">
+        <is>
+          <t>Infill panels</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>70 flat aluminium panels INCLUDED</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>EXCLUDED - 'Panels by others', 46.09 m2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="25" t="inlineStr">
+        <is>
+          <t>Element U-value</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>'glazing only ... non rebated'</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>'will only reach 1.8/1.9'</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="25" t="inlineStr">
+        <is>
+          <t>g-value (0.5-0.6 required)</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>no coating named, no g stated</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>0.66 STATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="25" t="inlineStr">
+        <is>
+          <t>Acoustic (Rw 32 dB on ED-06)</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>glazing only</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>'no formal acoustic test data'</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="25" t="inlineStr">
+        <is>
+          <t>LPS 1175 SR2 (ED-06)</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>not addressed</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>not addressed (PAS 24 offered instead)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="25" t="inlineStr">
+        <is>
+          <t>Access control</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>strike + latch + rectifier bundled in</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>excluded, PAS 24 maglock only</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="25" t="inlineStr">
+        <is>
+          <t>Finish</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>RAL 7035 throughout (spec: mill)</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>single colour throughout (spec: mill)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="25" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>ex works, no terms page at all</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>ex works; FOC only &lt;50 miles of Watford</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="25" t="inlineStr">
+        <is>
+          <t>Validity</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>none stated anywhere</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>30 days, ~26/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="25" t="inlineStr">
+        <is>
+          <t>Lead time</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>none stated</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>'confirmed on receipt of written order'</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="25" t="inlineStr">
+        <is>
+          <t>Warranty</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>none on the document</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>none on the document</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="61">
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="F56:I56"/>
+    <mergeCell ref="J56:M56"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="J47:M47"/>
+    <mergeCell ref="J27:L27"/>
+    <mergeCell ref="E33:L33"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="F48:I48"/>
+    <mergeCell ref="E42:L42"/>
+    <mergeCell ref="J50:M50"/>
+    <mergeCell ref="J46:M46"/>
+    <mergeCell ref="J51:M51"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="E39:L39"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="F49:I49"/>
+    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="E35:L35"/>
+    <mergeCell ref="J58:M58"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="J52:M52"/>
+    <mergeCell ref="J48:M48"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="F57:I57"/>
+    <mergeCell ref="E38:L38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="C30:L30"/>
+    <mergeCell ref="F54:I54"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="J57:M57"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E34:L34"/>
+    <mergeCell ref="E40:L40"/>
+    <mergeCell ref="J59:M59"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="J60:M60"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="F55:I55"/>
+    <mergeCell ref="F59:I59"/>
+    <mergeCell ref="E36:L36"/>
+    <mergeCell ref="F51:I51"/>
+    <mergeCell ref="J53:M53"/>
+    <mergeCell ref="F45:I45"/>
+    <mergeCell ref="J49:M49"/>
+    <mergeCell ref="J29:L29"/>
+    <mergeCell ref="J45:M45"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="J28:L28"/>
+    <mergeCell ref="J55:M55"/>
+    <mergeCell ref="E41:L41"/>
+    <mergeCell ref="F47:I47"/>
+    <mergeCell ref="J54:M54"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="E37:L37"/>
+    <mergeCell ref="F46:I46"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>